--- a/MMT_Flights_Selenium/test_data/passenger_data.xlsx
+++ b/MMT_Flights_Selenium/test_data/passenger_data.xlsx
@@ -5,16 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5cb9af0303145b3f/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wipro_training_work\python_coding\Capstone_Project\MMT_Flights_Selenium\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="8_{05A90147-5D3A-48C3-85B1-02A868BDEA77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D078E245-1458-412B-9ED4-6E7B083BBB35}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD2673B8-6092-403D-BC08-45985FCC4BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{D1813E3B-FABA-40F4-A5D8-BC60078A88AE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{D1813E3B-FABA-40F4-A5D8-BC60078A88AE}"/>
   </bookViews>
   <sheets>
     <sheet name="BookingData" sheetId="2" r:id="rId1"/>
-    <sheet name="PassengerData" sheetId="3" r:id="rId2"/>
+    <sheet name="PositiveFlights" sheetId="4" r:id="rId2"/>
+    <sheet name="PassengerData" sheetId="3" r:id="rId3"/>
+    <sheet name="NegativeFlights" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="31">
   <si>
     <t>Delhi</t>
   </si>
@@ -68,13 +70,73 @@
   </si>
   <si>
     <t>Fri Jun 19 2026</t>
+  </si>
+  <si>
+    <t>New Delhi</t>
+  </si>
+  <si>
+    <t>Bengaluru</t>
+  </si>
+  <si>
+    <t>expected_result</t>
+  </si>
+  <si>
+    <t>filter_type</t>
+  </si>
+  <si>
+    <t>non_stop</t>
+  </si>
+  <si>
+    <t>Filtered by Non-Stop</t>
+  </si>
+  <si>
+    <t>cheapest</t>
+  </si>
+  <si>
+    <t>Sorted by Price</t>
+  </si>
+  <si>
+    <t>Hyderabad</t>
+  </si>
+  <si>
+    <t>Chennai</t>
+  </si>
+  <si>
+    <t>morning</t>
+  </si>
+  <si>
+    <t>Filtered by Morning</t>
+  </si>
+  <si>
+    <t>expected_error</t>
+  </si>
+  <si>
+    <t>Bangalore</t>
+  </si>
+  <si>
+    <t>adults</t>
+  </si>
+  <si>
+    <t>infants</t>
+  </si>
+  <si>
+    <t>cannot be the same</t>
+  </si>
+  <si>
+    <t>Number of infants cannot be more than adults</t>
+  </si>
+  <si>
+    <t>Filtered by Air India</t>
+  </si>
+  <si>
+    <t>Air India</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,6 +152,32 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -99,7 +187,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -107,14 +195,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -466,6 +584,108 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A24F739-250B-4ECA-8BFD-30E5A6CE9718}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.77734375" customWidth="1"/>
+    <col min="2" max="2" width="23.21875" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" customWidth="1"/>
+    <col min="4" max="4" width="24.21875" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="4">
+        <v>46192</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="4">
+        <v>46195</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="4">
+        <v>46198</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="4">
+        <v>46201</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F3B2D9-A532-4C77-B5D2-649ED718116D}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -503,4 +723,73 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF5A86C5-6862-4586-B9FA-17CBDAF184E5}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" customWidth="1"/>
+    <col min="5" max="5" width="19.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="6">
+        <v>1</v>
+      </c>
+      <c r="D2" s="6">
+        <v>0</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="6">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6">
+        <v>2</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>